--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:22</t>
+          <t>2026-08-24 16:04:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:25</t>
+          <t>2026-08-24 16:04:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:28</t>
+          <t>2026-08-24 16:04:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:30</t>
+          <t>2026-08-24 16:04:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:30</t>
+          <t>2026-08-24 16:04:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:30</t>
+          <t>2026-08-24 16:04:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:30</t>
+          <t>2026-08-24 16:04:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:30</t>
+          <t>2026-08-24 16:04:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 15:03:30</t>
+          <t>2026-08-24 16:04:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:29</t>
+          <t>2026-08-24 16:23:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:31</t>
+          <t>2026-08-24 16:23:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:32</t>
+          <t>2026-08-24 16:23:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:04:33</t>
+          <t>2026-08-24 16:23:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:37</t>
+          <t>2026-08-24 16:41:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:40</t>
+          <t>2026-08-24 16:41:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:41</t>
+          <t>2026-08-24 16:41:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:43</t>
+          <t>2026-08-24 16:42:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:43</t>
+          <t>2026-08-24 16:42:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:43</t>
+          <t>2026-08-24 16:42:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:43</t>
+          <t>2026-08-24 16:42:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:43</t>
+          <t>2026-08-24 16:42:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:23:43</t>
+          <t>2026-08-24 16:42:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:56</t>
+          <t>2026-08-24 16:55:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:57</t>
+          <t>2026-08-24 16:55:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:41:59</t>
+          <t>2026-08-24 16:55:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:00</t>
+          <t>2026-08-24 16:55:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.16%11,884,000</t>
+          <t>10.12%11,884,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.16%</t>
+          <t>10.12%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.76%4,843,000</t>
+          <t>9.43%4,843,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.76%</t>
+          <t>9.43%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.82%20,300,000</t>
+          <t>7.83%20,300,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.82%</t>
+          <t>7.83%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.92%5,148,000</t>
+          <t>6.95%5,148,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.00%5,899,000</t>
+          <t>6.04%5,899,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.54%551</t>
+          <t>+0.72%6300</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>551</v>
+        <v>6300</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.99%25,387,000</t>
+          <t>5.03%2,226,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>25387000</v>
+        <v>2226000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.72%6300</t>
+          <t>-0.54%551</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6300</v>
+        <v>551</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.94%2,226,000</t>
+          <t>5.02%25,387,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>5.02%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2226000</v>
+        <v>25387000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.82%2,486,000</t>
+          <t>4.96%2,486,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.96%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.74%6,564,000</t>
+          <t>4.87%6,564,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.87%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,16 +1071,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.59%2,395,000</t>
+          <t>4.45%2,407,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2395000</v>
+        <v>2407000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.37%7,040,000</t>
+          <t>4.38%7,040,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.06%19,479,000</t>
+          <t>4.14%19,479,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>+6.01%123.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+6.01%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1135</v>
+        <v>123.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.88%9,624,000</t>
+          <t>3.97%89,518,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9624000</v>
+        <v>89518000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>0%1135</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2050</v>
+        <v>1135</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.77%4,671,848</t>
+          <t>3.92%9,624,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4671848</v>
+        <v>9624000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:28</t>
+          <t>2026-08-24 19:45:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+6.01%123.5</t>
+          <t>-9.89%2050</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+6.01%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>123.5</v>
+        <v>2050</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.62%87,518,000</t>
+          <t>3.44%4,671,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>87518000</v>
+        <v>4671848</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.92%5,498,000</t>
+          <t>2.87%5,498,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1502,16 +1502,16 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.24%410,900</t>
+          <t>2.08%383,900</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>410900</v>
+        <v>383900</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.42%2,264,000</t>
+          <t>1.39%2,264,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.93%11,275,450</t>
+          <t>0.97%11,275,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.83%2,477,000</t>
+          <t>0.86%2,477,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1797,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-5.2%547</t>
+          <t>+5.05%1145</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.50%2,424,000</t>
+          <t>0.53%1,301,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2424000</v>
+        <v>1301000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1860,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0%2650</t>
+          <t>-4.2%5365</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.45%477,000</t>
+          <t>0.49%255,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>477000</v>
+        <v>255000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.23%205.5</t>
+          <t>-5.2%547</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.43%5,917,000</t>
+          <t>0.48%2,424,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>5917000</v>
+        <v>2424000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,40 +1986,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5.05%1145</t>
+          <t>0%2650</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.43%1,101,000</t>
+          <t>0.45%477,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1101000</v>
+        <v>477000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,40 +2049,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.2%5365</t>
+          <t>+1.23%205.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.28%142,000</t>
+          <t>0.44%5,917,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>142000</v>
+        <v>5917000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.22%3,249,000</t>
+          <t>0.21%3,249,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:30</t>
+          <t>2026-08-24 19:45:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.20%483,000</t>
+          <t>0.21%483,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.11%1,741,000</t>
+          <t>0.12%1,741,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2606,38 +2606,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.8%97.1</t>
+          <t>-4.36%417</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>97.09999999999999</v>
+        <v>417</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.01%200,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2667,21 +2667,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-4.36%417</t>
+          <t>+0.95%3735</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>417</v>
+        <v>3735</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,21 +2728,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.95%3735</t>
+          <t>-0.12%82.4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3735</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2789,21 +2789,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.12%82.4</t>
+          <t>0%1435</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>82.40000000000001</v>
+        <v>1435</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2850,21 +2850,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%1435</t>
+          <t>-4.01%5385</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1435</v>
+        <v>5385</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,21 +2911,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>+1.09%325</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5385</v>
+        <v>325</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2972,21 +2972,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.09%325</t>
+          <t>-5.11%501</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-5.11%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>325</v>
+        <v>501</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3033,21 +3033,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-5.11%501</t>
+          <t>-4.8%97.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>501</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:31</t>
+          <t>2026-08-24 19:45:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:32</t>
+          <t>2026-08-24 19:45:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:32</t>
+          <t>2026-08-24 19:45:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:32</t>
+          <t>2026-08-24 19:45:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:32</t>
+          <t>2026-08-24 19:45:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:32</t>
+          <t>2026-08-24 19:45:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:55:32</t>
+          <t>2026-08-24 19:45:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:08</t>
+          <t>2026-08-24 19:58:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:12</t>
+          <t>2026-08-24 19:58:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:13</t>
+          <t>2026-08-24 19:58:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:14</t>
+          <t>2026-08-24 19:58:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:14</t>
+          <t>2026-08-24 19:58:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:14</t>
+          <t>2026-08-24 19:58:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:14</t>
+          <t>2026-08-24 19:58:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:14</t>
+          <t>2026-08-24 19:58:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 19:45:14</t>
+          <t>2026-08-24 19:58:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:40</t>
+          <t>2026-08-24 20:02:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:41</t>
+          <t>2026-08-24 20:02:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:42</t>
+          <t>2026-08-24 20:02:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:44</t>
+          <t>2026-08-24 20:02:19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:44</t>
+          <t>2026-08-24 20:02:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:44</t>
+          <t>2026-08-24 20:02:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:44</t>
+          <t>2026-08-24 20:02:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:44</t>
+          <t>2026-08-24 20:02:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 19:58:44</t>
+          <t>2026-08-24 20:02:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:15</t>
+          <t>2026-08-24 23:03:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:16</t>
+          <t>2026-08-24 23:03:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:18</t>
+          <t>2026-08-24 23:03:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:19</t>
+          <t>2026-08-24 23:03:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:19</t>
+          <t>2026-08-24 23:03:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:19</t>
+          <t>2026-08-24 23:03:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:19</t>
+          <t>2026-08-24 23:03:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:19</t>
+          <t>2026-08-24 23:03:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 20:02:19</t>
+          <t>2026-08-24 23:03:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
